--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.81625473918521</v>
+        <v>5.495141395117597</v>
       </c>
       <c r="D2" t="n">
-        <v>33.68577539301814</v>
+        <v>5.473938501365448</v>
       </c>
       <c r="E2" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F2" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.15434301698941</v>
+        <v>5.387580740260779</v>
       </c>
       <c r="D3" t="n">
-        <v>33.04015344250235</v>
+        <v>5.369024934406633</v>
       </c>
       <c r="E3" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F3" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.25738712225579</v>
+        <v>6.379325407366567</v>
       </c>
       <c r="D4" t="n">
-        <v>39.17705881645333</v>
+        <v>6.366272057673667</v>
       </c>
       <c r="E4" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F4" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.92446077810974</v>
+        <v>4.537724876442834</v>
       </c>
       <c r="D5" t="n">
-        <v>27.83154253735085</v>
+        <v>4.522625662319513</v>
       </c>
       <c r="E5" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F5" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.36652260819014</v>
+        <v>5.584559923830898</v>
       </c>
       <c r="D6" t="n">
-        <v>34.33496308399715</v>
+        <v>5.579431501149537</v>
       </c>
       <c r="E6" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F6" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.07154484035446</v>
+        <v>6.511626036557599</v>
       </c>
       <c r="D7" t="n">
-        <v>40.05121863909341</v>
+        <v>6.508323028852678</v>
       </c>
       <c r="E7" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F7" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.11600970864056</v>
+        <v>3.756351577654091</v>
       </c>
       <c r="D8" t="n">
-        <v>23.16574018700684</v>
+        <v>3.764432780388611</v>
       </c>
       <c r="E8" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F8" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83677882577977</v>
+        <v>5.823476559189213</v>
       </c>
       <c r="D9" t="n">
-        <v>35.86858255265237</v>
+        <v>5.82864466480601</v>
       </c>
       <c r="E9" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F9" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.87166556243334</v>
+        <v>4.529145653895418</v>
       </c>
       <c r="D10" t="n">
-        <v>27.95523213214081</v>
+        <v>4.542725221472882</v>
       </c>
       <c r="E10" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F10" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.04349417564502</v>
+        <v>6.344567803542317</v>
       </c>
       <c r="D11" t="n">
-        <v>39.16336017305026</v>
+        <v>6.364046028120669</v>
       </c>
       <c r="E11" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F11" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.56802603330488</v>
+        <v>6.429804230412044</v>
       </c>
       <c r="D12" t="n">
-        <v>39.69725295354471</v>
+        <v>6.450803604951015</v>
       </c>
       <c r="E12" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F12" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.46729284255247</v>
+        <v>9.013435086914777</v>
       </c>
       <c r="D13" t="n">
-        <v>55.59785389519612</v>
+        <v>9.034651257969371</v>
       </c>
       <c r="E13" t="n">
-        <v>7.855340721306142</v>
+        <v>1.276492867212248</v>
       </c>
       <c r="F13" t="n">
-        <v>7.888979916599009</v>
+        <v>1.281959236447339</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
